--- a/src/data/dados.xlsx
+++ b/src/data/dados.xlsx
@@ -20,31 +20,86 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t xml:space="preserve">Empresa</t>
   </si>
   <si>
+    <t xml:space="preserve">Acao</t>
+  </si>
+  <si>
     <t xml:space="preserve">CPF</t>
   </si>
   <si>
     <t xml:space="preserve">Carteirinha</t>
   </si>
   <si>
-    <t xml:space="preserve">codigo_empresa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cod_cart</t>
+    <t xml:space="preserve">Matricula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataNasc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sexo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EstadoCivil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataAdm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endereco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bairro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cod_empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cod_un</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cod_plano</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -66,6 +121,13 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -109,12 +171,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -241,45 +319,131 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="15.9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>11122233344</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>11121233355</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
